--- a/GearSage-client/pkgGear/data_raw/ark_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/ark_rod_import.xlsx
@@ -647,12 +647,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1072,10 +1075,11 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3365,7 +3369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR227"/>
+  <dimension ref="A1:AS227"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="5"/>
@@ -3397,6 +3401,7 @@
     <col width="23" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="14" customWidth="1" min="42" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3612,10 +3617,15 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>product_technical</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>Extra Spec 1</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Extra Spec 2</t>
         </is>
@@ -3756,12 +3766,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ2" s="3" t="inlineStr">
+      <c r="AQ2" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR2" s="3" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659024; Shopify variant id: 42643162235120; Availability: out of stock</t>
         </is>
@@ -3902,12 +3917,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AQ3" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659031; Shopify variant id: 42643162267888; Availability: out of stock</t>
         </is>
@@ -4048,12 +4068,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AQ4" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659048; Shopify variant id: 42643162300656; Availability: out of stock</t>
         </is>
@@ -4194,12 +4219,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ5" s="3" t="inlineStr">
+      <c r="AQ5" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659055; Shopify variant id: 42643162333424; Availability: out of stock</t>
         </is>
@@ -4340,12 +4370,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ6" s="3" t="inlineStr">
+      <c r="AQ6" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR6" s="3" t="inlineStr">
+      <c r="AS6" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659062; Shopify variant id: 42643162398960; Availability: out of stock</t>
         </is>
@@ -4486,12 +4521,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ7" s="3" t="inlineStr">
+      <c r="AQ7" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR7" s="3" t="inlineStr">
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659079; Shopify variant id: 42643162431728; Availability: out of stock</t>
         </is>
@@ -4632,12 +4672,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ8" s="3" t="inlineStr">
+      <c r="AQ8" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR8" s="3" t="inlineStr">
+      <c r="AS8" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659086; Shopify variant id: 42643162464496; Availability: out of stock</t>
         </is>
@@ -4778,12 +4823,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ9" s="3" t="inlineStr">
+      <c r="AQ9" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR9" s="3" t="inlineStr">
+      <c r="AS9" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659093; Shopify variant id: 42643162497264; Availability: out of stock</t>
         </is>
@@ -4924,12 +4974,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ10" s="3" t="inlineStr">
+      <c r="AQ10" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR10" s="3" t="inlineStr">
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659109; Shopify variant id: 42643162530032; Availability: out of stock</t>
         </is>
@@ -5070,12 +5125,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ11" s="3" t="inlineStr">
+      <c r="AQ11" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR11" s="3" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR11" s="3" t="inlineStr">
+      <c r="AS11" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659116; Shopify variant id: 42643162562800; Availability: out of stock</t>
         </is>
@@ -5216,12 +5276,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ12" s="4" t="inlineStr">
+      <c r="AQ12" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR12" s="4" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR12" s="4" t="inlineStr">
+      <c r="AS12" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964658980; Shopify variant id: 42643162005744; Availability: out of stock</t>
         </is>
@@ -5362,12 +5427,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ13" s="4" t="inlineStr">
+      <c r="AQ13" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR13" s="4" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR13" s="4" t="inlineStr">
+      <c r="AS13" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659000; Shopify variant id: 43440023830768; Availability: out of stock</t>
         </is>
@@ -5508,12 +5578,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ14" s="4" t="inlineStr">
+      <c r="AQ14" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR14" s="4" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR14" s="4" t="inlineStr">
+      <c r="AS14" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964658997; Shopify variant id: 43440023798000; Availability: out of stock</t>
         </is>
@@ -5654,12 +5729,17 @@
           <t>The Reinforcer Series is the new flagship of ARK Rods. The top of line un-sanded rod blank is made of 46T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers and constructed by our ARK high pressure carbon-fiber rolling technology. Not only you can see our logo through the whole blank but also it makes the rod incredible light, stronger and sensitive. It also come with Fuji PTS/TVS reel seat with soft touch layer, Titanium guides, portugal AAAA grade cork handle and lifetime warranty.</t>
         </is>
       </c>
-      <c r="AQ15" s="4" t="inlineStr">
+      <c r="AQ15" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji PTS/TVS reel seat</t>
+        </is>
+      </c>
+      <c r="AR15" s="4" t="inlineStr">
         <is>
           <t>Fuji components / Titanium guides / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR15" s="4" t="inlineStr">
+      <c r="AS15" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659017; Shopify variant id: 42643162104048; Availability: out of stock</t>
         </is>
@@ -5802,12 +5882,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ16" s="3" t="inlineStr">
+      <c r="AQ16" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR16" s="3" t="inlineStr">
+      <c r="AS16" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964661881; Shopify variant id: 42643164987632; Availability: out of stock</t>
         </is>
@@ -5950,12 +6035,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ17" s="3" t="inlineStr">
+      <c r="AQ17" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR17" s="3" t="inlineStr">
+      <c r="AS17" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964661898; Shopify variant id: 43440080748784; Availability: out of stock</t>
         </is>
@@ -6098,12 +6188,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ18" s="3" t="inlineStr">
+      <c r="AQ18" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR18" s="3" t="inlineStr">
+      <c r="AS18" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659826; Shopify variant id: 43440080912624; Availability: out of stock</t>
         </is>
@@ -6246,12 +6341,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ19" s="3" t="inlineStr">
+      <c r="AQ19" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR19" s="3" t="inlineStr">
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964661904; Shopify variant id: 43440081010928; Availability: out of stock</t>
         </is>
@@ -6394,12 +6494,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ20" s="3" t="inlineStr">
+      <c r="AQ20" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR20" s="3" t="inlineStr">
+      <c r="AS20" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659833; Shopify variant id: 43440081240304; Availability: out of stock</t>
         </is>
@@ -6542,12 +6647,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ21" s="3" t="inlineStr">
+      <c r="AQ21" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR21" s="3" t="inlineStr">
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659840; Shopify variant id: 43440081338608; Availability: out of stock</t>
         </is>
@@ -6690,12 +6800,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ22" s="3" t="inlineStr">
+      <c r="AQ22" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR22" s="3" t="inlineStr">
+      <c r="AS22" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659857; Shopify variant id: 43440081502448; Availability: out of stock</t>
         </is>
@@ -6838,12 +6953,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ23" s="3" t="inlineStr">
+      <c r="AQ23" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR23" s="3" t="inlineStr">
+      <c r="AS23" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659864; Shopify variant id: 43445278081264; Availability: out of stock</t>
         </is>
@@ -6986,12 +7106,17 @@
 ARK Invoker Limited Edition Casting Rods deliver all of the performance of the original Invoker series, but in a select range of lengths, tapers, and quantities. Built using unsanded, 40T HM carbon fiber blanks, the ARK Invoker Limited Edition Casting Rods feature nano tube reinforcements throughout each layer of carbon fiber, and are constructed using ARK's HPCR (High Pressure Carbon Fiber Rolling) technology to deliver a lightweight, yet incredibly tough design.</t>
         </is>
       </c>
-      <c r="AQ24" s="3" t="inlineStr">
+      <c r="AQ24" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept Alconite guides</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / lifetime warranty</t>
         </is>
       </c>
-      <c r="AR24" s="3" t="inlineStr">
+      <c r="AS24" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964659871; Shopify variant id: 43445278114032; Availability: out of stock</t>
         </is>
@@ -7136,12 +7261,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ25" s="4" t="inlineStr">
+      <c r="AQ25" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR25" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR25" s="4" t="inlineStr">
+      <c r="AS25" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006177; Shopify variant id: 47024318120176; Availability: out of stock</t>
         </is>
@@ -7286,12 +7416,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ26" s="4" t="inlineStr">
+      <c r="AQ26" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR26" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR26" s="4" t="inlineStr">
+      <c r="AS26" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006184; Shopify variant id: 47024318152944; Availability: out of stock</t>
         </is>
@@ -7436,12 +7571,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ27" s="4" t="inlineStr">
+      <c r="AQ27" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR27" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR27" s="4" t="inlineStr">
+      <c r="AS27" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006191; Shopify variant id: 47024318185712; Availability: out of stock</t>
         </is>
@@ -7586,12 +7726,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ28" s="3" t="inlineStr">
+      <c r="AQ28" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR28" s="3" t="inlineStr">
+      <c r="AS28" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006207; Shopify variant id: 47024390930672; Availability: out of stock</t>
         </is>
@@ -7736,12 +7881,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ29" s="3" t="inlineStr">
+      <c r="AQ29" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR29" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR29" s="3" t="inlineStr">
+      <c r="AS29" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006214; Shopify variant id: 47024390963440; Availability: out of stock</t>
         </is>
@@ -7886,12 +8036,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ30" s="3" t="inlineStr">
+      <c r="AQ30" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR30" s="3" t="inlineStr">
+      <c r="AS30" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006221; Shopify variant id: 47024390996208; Availability: out of stock</t>
         </is>
@@ -8036,12 +8191,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ31" s="3" t="inlineStr">
+      <c r="AQ31" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR31" s="3" t="inlineStr">
+      <c r="AS31" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006238; Shopify variant id: 47024391028976; Availability: out of stock</t>
         </is>
@@ -8186,12 +8346,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ32" s="3" t="inlineStr">
+      <c r="AQ32" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR32" s="3" t="inlineStr">
+      <c r="AS32" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006245; Shopify variant id: 47024391061744; Availability: out of stock</t>
         </is>
@@ -8336,12 +8501,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ33" s="3" t="inlineStr">
+      <c r="AQ33" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR33" s="3" t="inlineStr">
+      <c r="AS33" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006252; Shopify variant id: 47024391094512; Availability: out of stock</t>
         </is>
@@ -8486,12 +8656,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ34" s="3" t="inlineStr">
+      <c r="AQ34" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR34" s="3" t="inlineStr">
+      <c r="AS34" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006269; Shopify variant id: 47024391127280; Availability: out of stock</t>
         </is>
@@ -8636,12 +8811,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ35" s="3" t="inlineStr">
+      <c r="AQ35" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR35" s="3" t="inlineStr">
+      <c r="AS35" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006276; Shopify variant id: 47024391160048; Availability: out of stock</t>
         </is>
@@ -8786,12 +8966,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ36" s="3" t="inlineStr">
+      <c r="AQ36" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR36" s="3" t="inlineStr">
+      <c r="AS36" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006283; Shopify variant id: 47024391192816; Availability: out of stock</t>
         </is>
@@ -8936,12 +9121,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ37" s="3" t="inlineStr">
+      <c r="AQ37" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR37" s="3" t="inlineStr">
+      <c r="AS37" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006290; Shopify variant id: 47024391225584; Availability: out of stock</t>
         </is>
@@ -9086,12 +9276,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ38" s="3" t="inlineStr">
+      <c r="AQ38" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR38" s="3" t="inlineStr">
+      <c r="AS38" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006306; Shopify variant id: 47024391258352; Availability: out of stock</t>
         </is>
@@ -9236,12 +9431,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ39" s="3" t="inlineStr">
+      <c r="AQ39" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR39" s="3" t="inlineStr">
+      <c r="AS39" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006313; Shopify variant id: 47024391291120; Availability: out of stock</t>
         </is>
@@ -9386,12 +9586,17 @@
 Every Sniper II Series rod is backed by a 5-year limited warranty , delivering the reliability and quality you can trust.</t>
         </is>
       </c>
-      <c r="AQ40" s="3" t="inlineStr">
+      <c r="AQ40" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR40" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR40" s="3" t="inlineStr">
+      <c r="AS40" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006320; Shopify variant id: 47024391323888; Availability: out of stock</t>
         </is>
@@ -9540,12 +9745,17 @@
 Each rod comes with a custom rod sleeve.</t>
         </is>
       </c>
-      <c r="AQ41" s="4" t="inlineStr">
+      <c r="AQ41" s="7" t="inlineStr">
+        <is>
+          <t>ARK Titanium Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR41" s="4" t="inlineStr">
         <is>
           <t>Titanium guides / NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR41" s="4" t="inlineStr">
+      <c r="AS41" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005774; Shopify variant id: 46990436696304; Availability: out of stock</t>
         </is>
@@ -9694,12 +9904,17 @@
 Each rod comes with a custom rod sleeve.</t>
         </is>
       </c>
-      <c r="AQ42" s="4" t="inlineStr">
+      <c r="AQ42" s="7" t="inlineStr">
+        <is>
+          <t>ARK Titanium Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR42" s="4" t="inlineStr">
         <is>
           <t>Titanium guides / NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR42" s="4" t="inlineStr">
+      <c r="AS42" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005767; Shopify variant id: 46990436729072; Availability: out of stock</t>
         </is>
@@ -9848,12 +10063,17 @@
 Each rod comes with a custom rod sleeve.</t>
         </is>
       </c>
-      <c r="AQ43" s="4" t="inlineStr">
+      <c r="AQ43" s="7" t="inlineStr">
+        <is>
+          <t>ARK Titanium Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR43" s="4" t="inlineStr">
         <is>
           <t>Titanium guides / NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR43" s="4" t="inlineStr">
+      <c r="AS43" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077003787; Shopify variant id: 46715290484976; Availability: out of stock</t>
         </is>
@@ -10002,12 +10222,17 @@
 Each rod comes with a custom rod sleeve.</t>
         </is>
       </c>
-      <c r="AQ44" s="4" t="inlineStr">
+      <c r="AQ44" s="7" t="inlineStr">
+        <is>
+          <t>ARK Titanium Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR44" s="4" t="inlineStr">
         <is>
           <t>Titanium guides / NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR44" s="4" t="inlineStr">
+      <c r="AS44" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077003794; Shopify variant id: 46715290517744; Availability: out of stock</t>
         </is>
@@ -10156,12 +10381,17 @@
 Each rod comes with a custom rod sleeve.</t>
         </is>
       </c>
-      <c r="AQ45" s="4" t="inlineStr">
+      <c r="AQ45" s="7" t="inlineStr">
+        <is>
+          <t>ARK Titanium Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR45" s="4" t="inlineStr">
         <is>
           <t>Titanium guides / NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR45" s="4" t="inlineStr">
+      <c r="AS45" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077003817; Shopify variant id: 46715290583280; Availability: out of stock</t>
         </is>
@@ -10310,12 +10540,17 @@
 Each rod comes with a custom rod sleeve.</t>
         </is>
       </c>
-      <c r="AQ46" s="4" t="inlineStr">
+      <c r="AQ46" s="7" t="inlineStr">
+        <is>
+          <t>ARK Titanium Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR46" s="4" t="inlineStr">
         <is>
           <t>Titanium guides / NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR46" s="4" t="inlineStr">
+      <c r="AS46" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077003800; Shopify variant id: 46715290550512; Availability: out of stock</t>
         </is>
@@ -10456,12 +10691,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ47" s="3" t="inlineStr">
+      <c r="AQ47" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR47" s="3" t="inlineStr">
+      <c r="AS47" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662321; Shopify variant id: 42643196510448; Availability: out of stock</t>
         </is>
@@ -10602,12 +10842,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ48" s="3" t="inlineStr">
+      <c r="AQ48" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR48" s="3" t="inlineStr">
+      <c r="AS48" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662338; Shopify variant id: 42643196543216; Availability: out of stock</t>
         </is>
@@ -10748,12 +10993,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ49" s="3" t="inlineStr">
+      <c r="AQ49" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR49" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR49" s="3" t="inlineStr">
+      <c r="AS49" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662345; Shopify variant id: 42643196575984; Availability: out of stock</t>
         </is>
@@ -10894,12 +11144,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ50" s="3" t="inlineStr">
+      <c r="AQ50" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR50" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR50" s="3" t="inlineStr">
+      <c r="AS50" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662352; Shopify variant id: 42643196608752; Availability: out of stock</t>
         </is>
@@ -11040,12 +11295,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ51" s="3" t="inlineStr">
+      <c r="AQ51" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR51" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR51" s="3" t="inlineStr">
+      <c r="AS51" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662369; Shopify variant id: 42643196641520; Availability: out of stock</t>
         </is>
@@ -11186,12 +11446,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ52" s="3" t="inlineStr">
+      <c r="AQ52" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR52" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR52" s="3" t="inlineStr">
+      <c r="AS52" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662628; Shopify variant id: 42643196674288; Availability: out of stock</t>
         </is>
@@ -11332,12 +11597,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ53" s="3" t="inlineStr">
+      <c r="AQ53" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR53" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR53" s="3" t="inlineStr">
+      <c r="AS53" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662376; Shopify variant id: 42643196707056; Availability: out of stock</t>
         </is>
@@ -11478,12 +11748,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ54" s="3" t="inlineStr">
+      <c r="AQ54" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR54" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR54" s="3" t="inlineStr">
+      <c r="AS54" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662383; Shopify variant id: 42643196739824; Availability: out of stock</t>
         </is>
@@ -11624,12 +11899,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ55" s="3" t="inlineStr">
+      <c r="AQ55" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR55" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR55" s="3" t="inlineStr">
+      <c r="AS55" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662390; Shopify variant id: 42643196772592; Availability: out of stock</t>
         </is>
@@ -11770,12 +12050,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ56" s="3" t="inlineStr">
+      <c r="AQ56" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR56" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR56" s="3" t="inlineStr">
+      <c r="AS56" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662406; Shopify variant id: 42643196805360; Availability: out of stock</t>
         </is>
@@ -11916,12 +12201,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ57" s="3" t="inlineStr">
+      <c r="AQ57" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR57" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR57" s="3" t="inlineStr">
+      <c r="AS57" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662581; Shopify variant id: 42643196838128; Availability: out of stock</t>
         </is>
@@ -12062,12 +12352,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ58" s="3" t="inlineStr">
+      <c r="AQ58" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR58" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR58" s="3" t="inlineStr">
+      <c r="AS58" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662598; Shopify variant id: 42643196870896; Availability: out of stock</t>
         </is>
@@ -12208,12 +12503,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ59" s="3" t="inlineStr">
+      <c r="AQ59" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR59" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR59" s="3" t="inlineStr">
+      <c r="AS59" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662604; Shopify variant id: 42643196903664; Availability: out of stock</t>
         </is>
@@ -12354,12 +12654,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ60" s="3" t="inlineStr">
+      <c r="AQ60" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR60" s="3" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR60" s="3" t="inlineStr">
+      <c r="AS60" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662611; Shopify variant id: 42643196936432; Availability: out of stock</t>
         </is>
@@ -12500,12 +12805,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ61" s="4" t="inlineStr">
+      <c r="AQ61" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR61" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR61" s="4" t="inlineStr">
+      <c r="AS61" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964662291; Shopify variant id: 42643166298352; Availability: out of stock</t>
         </is>
@@ -12646,12 +12956,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ62" s="4" t="inlineStr">
+      <c r="AQ62" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR62" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR62" s="4" t="inlineStr">
+      <c r="AS62" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964662307; Shopify variant id: 42643166331120; Availability: out of stock</t>
         </is>
@@ -12792,12 +13107,17 @@
           <t>The Brand New Essence series rods are made of 40T HM carbon-fiber enhanced with carbon nano tube in between the carbon-fiber layers. AAA grade full cork handle, Fuji K-concept tangle-free guides with Fazlite rings, ARK designed reel seat and 5-Year limited warranty.</t>
         </is>
       </c>
-      <c r="AQ63" s="4" t="inlineStr">
+      <c r="AQ63" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR63" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR63" s="4" t="inlineStr">
+      <c r="AS63" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964662314; Shopify variant id: 43440025796848; Availability: out of stock</t>
         </is>
@@ -12944,12 +13264,17 @@
 3A Grade Full Cork Handle - Ergonomic and comfortable for all-day fishing</t>
         </is>
       </c>
-      <c r="AQ64" s="3" t="inlineStr">
+      <c r="AQ64" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR64" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR64" s="3" t="inlineStr">
+      <c r="AS64" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002353; Shopify variant id: 46715090469104; Availability: out of stock</t>
         </is>
@@ -13096,12 +13421,17 @@
 3A Grade Full Cork Handle - Ergonomic and comfortable for all-day fishing</t>
         </is>
       </c>
-      <c r="AQ65" s="3" t="inlineStr">
+      <c r="AQ65" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR65" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR65" s="3" t="inlineStr">
+      <c r="AS65" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002360; Shopify variant id: 46715090501872; Availability: out of stock</t>
         </is>
@@ -13248,12 +13578,17 @@
 3A Grade Full Cork Handle - Ergonomic and comfortable for all-day fishing</t>
         </is>
       </c>
-      <c r="AQ66" s="3" t="inlineStr">
+      <c r="AQ66" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR66" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR66" s="3" t="inlineStr">
+      <c r="AS66" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002377; Shopify variant id: 46715090534640; Availability: out of stock</t>
         </is>
@@ -13400,12 +13735,17 @@
 3A Grade Full Cork Handle - Ergonomic and comfortable for all-day fishing</t>
         </is>
       </c>
-      <c r="AQ67" s="3" t="inlineStr">
+      <c r="AQ67" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR67" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR67" s="3" t="inlineStr">
+      <c r="AS67" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002384; Shopify variant id: 46715090567408; Availability: out of stock</t>
         </is>
@@ -13552,12 +13892,17 @@
 3A Grade Full Cork Handle - Ergonomic and comfortable for all-day fishing</t>
         </is>
       </c>
-      <c r="AQ68" s="3" t="inlineStr">
+      <c r="AQ68" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR68" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR68" s="3" t="inlineStr">
+      <c r="AS68" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002391; Shopify variant id: 46715090600176; Availability: out of stock</t>
         </is>
@@ -13704,12 +14049,17 @@
 3A Grade Full Cork Handle - Ergonomic and comfortable for all-day fishing</t>
         </is>
       </c>
-      <c r="AQ69" s="3" t="inlineStr">
+      <c r="AQ69" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR69" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR69" s="3" t="inlineStr">
+      <c r="AS69" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002407; Shopify variant id: 46715090632944; Availability: out of stock</t>
         </is>
@@ -13856,12 +14206,17 @@
 3A Grade Full Cork Handle - Ergonomic and comfortable for all-day fishing</t>
         </is>
       </c>
-      <c r="AQ70" s="3" t="inlineStr">
+      <c r="AQ70" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR70" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR70" s="3" t="inlineStr">
+      <c r="AS70" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002414; Shopify variant id: 46715090665712; Availability: out of stock</t>
         </is>
@@ -14007,12 +14362,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ71" s="4" t="inlineStr">
+      <c r="AQ71" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR71" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR71" s="4" t="inlineStr">
+      <c r="AS71" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002759; Shopify variant id: 45548235882736; Availability: out of stock</t>
         </is>
@@ -14158,12 +14518,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ72" s="4" t="inlineStr">
+      <c r="AQ72" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR72" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR72" s="4" t="inlineStr">
+      <c r="AS72" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002766; Shopify variant id: 45548235915504; Availability: out of stock</t>
         </is>
@@ -14309,12 +14674,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ73" s="3" t="inlineStr">
+      <c r="AQ73" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR73" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR73" s="3" t="inlineStr">
+      <c r="AS73" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002773; Shopify variant id: 45548222120176; Availability: out of stock</t>
         </is>
@@ -14460,12 +14830,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ74" s="3" t="inlineStr">
+      <c r="AQ74" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR74" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR74" s="3" t="inlineStr">
+      <c r="AS74" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002780; Shopify variant id: 45548222152944; Availability: out of stock</t>
         </is>
@@ -14611,12 +14986,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ75" s="3" t="inlineStr">
+      <c r="AQ75" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR75" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR75" s="3" t="inlineStr">
+      <c r="AS75" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002797; Shopify variant id: 45548222185712; Availability: out of stock</t>
         </is>
@@ -14762,12 +15142,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ76" s="3" t="inlineStr">
+      <c r="AQ76" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR76" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR76" s="3" t="inlineStr">
+      <c r="AS76" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002803; Shopify variant id: 45548222218480; Availability: out of stock</t>
         </is>
@@ -14913,12 +15298,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ77" s="3" t="inlineStr">
+      <c r="AQ77" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR77" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR77" s="3" t="inlineStr">
+      <c r="AS77" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002810; Shopify variant id: 45548222251248; Availability: out of stock</t>
         </is>
@@ -15064,12 +15454,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ78" s="3" t="inlineStr">
+      <c r="AQ78" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR78" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR78" s="3" t="inlineStr">
+      <c r="AS78" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002827; Shopify variant id: 45548222284016; Availability: out of stock</t>
         </is>
@@ -15215,12 +15610,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ79" s="3" t="inlineStr">
+      <c r="AQ79" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR79" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR79" s="3" t="inlineStr">
+      <c r="AS79" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002834; Shopify variant id: 45548222316784; Availability: out of stock</t>
         </is>
@@ -15366,12 +15766,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ80" s="3" t="inlineStr">
+      <c r="AQ80" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR80" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR80" s="3" t="inlineStr">
+      <c r="AS80" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002841; Shopify variant id: 45548222349552; Availability: out of stock</t>
         </is>
@@ -15517,12 +15922,17 @@
 5 Year Limited Warranty.</t>
         </is>
       </c>
-      <c r="AQ81" s="3" t="inlineStr">
+      <c r="AQ81" s="6" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR81" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR81" s="3" t="inlineStr">
+      <c r="AS81" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002858; Shopify variant id: 45548222382320; Availability: out of stock</t>
         </is>
@@ -15665,12 +16075,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ82" s="4" t="inlineStr">
+      <c r="AQ82" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR82" s="4" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR82" s="4" t="inlineStr">
+      <c r="AS82" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006481; Shopify variant id: 47843871523056; Availability: out of stock</t>
         </is>
@@ -15813,12 +16228,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ83" s="4" t="inlineStr">
+      <c r="AQ83" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR83" s="4" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR83" s="4" t="inlineStr">
+      <c r="AS83" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006498; Shopify variant id: 47843871555824; Availability: out of stock</t>
         </is>
@@ -15961,12 +16381,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ84" s="4" t="inlineStr">
+      <c r="AQ84" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR84" s="4" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR84" s="4" t="inlineStr">
+      <c r="AS84" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000588; Shopify variant id: 44167368540400; Availability: out of stock</t>
         </is>
@@ -16109,12 +16534,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ85" s="4" t="inlineStr">
+      <c r="AQ85" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR85" s="4" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR85" s="4" t="inlineStr">
+      <c r="AS85" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006504; Shopify variant id: 47843871588592; Availability: out of stock</t>
         </is>
@@ -16257,12 +16687,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ86" s="4" t="inlineStr">
+      <c r="AQ86" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR86" s="4" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR86" s="4" t="inlineStr">
+      <c r="AS86" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000595; Shopify variant id: 44167368573168; Availability: out of stock</t>
         </is>
@@ -16405,12 +16840,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ87" s="4" t="inlineStr">
+      <c r="AQ87" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR87" s="4" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR87" s="4" t="inlineStr">
+      <c r="AS87" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000601; Shopify variant id: 44167368605936; Availability: out of stock</t>
         </is>
@@ -16553,12 +16993,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ88" s="4" t="inlineStr">
+      <c r="AQ88" s="7" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR88" s="4" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR88" s="4" t="inlineStr">
+      <c r="AS88" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000618; Shopify variant id: 44167368638704; Availability: out of stock</t>
         </is>
@@ -16701,12 +17146,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ89" s="3" t="inlineStr">
+      <c r="AQ89" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR89" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR89" s="3" t="inlineStr">
+      <c r="AS89" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000847; Shopify variant id: 44169077915888; Availability: out of stock</t>
         </is>
@@ -16849,12 +17299,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ90" s="3" t="inlineStr">
+      <c r="AQ90" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR90" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR90" s="3" t="inlineStr">
+      <c r="AS90" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002186; Shopify variant id: 46699291476208; Availability: out of stock</t>
         </is>
@@ -16997,12 +17452,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ91" s="3" t="inlineStr">
+      <c r="AQ91" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR91" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR91" s="3" t="inlineStr">
+      <c r="AS91" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000885; Shopify variant id: 44169078046960; Availability: out of stock</t>
         </is>
@@ -17145,12 +17605,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ92" s="3" t="inlineStr">
+      <c r="AQ92" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR92" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR92" s="3" t="inlineStr">
+      <c r="AS92" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000854; Shopify variant id: 44169077948656; Availability: out of stock</t>
         </is>
@@ -17293,12 +17758,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ93" s="3" t="inlineStr">
+      <c r="AQ93" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR93" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR93" s="3" t="inlineStr">
+      <c r="AS93" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000625; Shopify variant id: 44167367655664; Availability: out of stock</t>
         </is>
@@ -17441,12 +17911,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ94" s="3" t="inlineStr">
+      <c r="AQ94" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR94" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR94" s="3" t="inlineStr">
+      <c r="AS94" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000632; Shopify variant id: 44167367688432; Availability: out of stock</t>
         </is>
@@ -17589,12 +18064,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ95" s="3" t="inlineStr">
+      <c r="AQ95" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR95" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR95" s="3" t="inlineStr">
+      <c r="AS95" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000649; Shopify variant id: 44167367721200; Availability: out of stock</t>
         </is>
@@ -17737,12 +18217,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ96" s="3" t="inlineStr">
+      <c r="AQ96" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR96" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR96" s="3" t="inlineStr">
+      <c r="AS96" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000656; Shopify variant id: 44167367753968; Availability: out of stock</t>
         </is>
@@ -17885,12 +18370,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ97" s="3" t="inlineStr">
+      <c r="AQ97" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR97" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR97" s="3" t="inlineStr">
+      <c r="AS97" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000663; Shopify variant id: 44167367786736; Availability: out of stock</t>
         </is>
@@ -18033,12 +18523,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ98" s="3" t="inlineStr">
+      <c r="AQ98" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR98" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR98" s="3" t="inlineStr">
+      <c r="AS98" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000830; Shopify variant id: 44169077883120; Availability: out of stock</t>
         </is>
@@ -18181,12 +18676,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ99" s="3" t="inlineStr">
+      <c r="AQ99" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR99" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR99" s="3" t="inlineStr">
+      <c r="AS99" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000670; Shopify variant id: 44167367819504; Availability: out of stock</t>
         </is>
@@ -18329,12 +18829,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ100" s="3" t="inlineStr">
+      <c r="AQ100" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR100" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR100" s="3" t="inlineStr">
+      <c r="AS100" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000694; Shopify variant id: 44167367885040; Availability: out of stock</t>
         </is>
@@ -18477,12 +18982,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ101" s="3" t="inlineStr">
+      <c r="AQ101" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR101" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR101" s="3" t="inlineStr">
+      <c r="AS101" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000878; Shopify variant id: 44169078014192; Availability: out of stock</t>
         </is>
@@ -18625,12 +19135,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ102" s="3" t="inlineStr">
+      <c r="AQ102" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR102" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR102" s="3" t="inlineStr">
+      <c r="AS102" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000687; Shopify variant id: 44167367852272; Availability: out of stock</t>
         </is>
@@ -18773,12 +19288,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ103" s="3" t="inlineStr">
+      <c r="AQ103" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR103" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR103" s="3" t="inlineStr">
+      <c r="AS103" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000700; Shopify variant id: 44167367917808; Availability: out of stock</t>
         </is>
@@ -18921,12 +19441,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ104" s="3" t="inlineStr">
+      <c r="AQ104" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR104" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR104" s="3" t="inlineStr">
+      <c r="AS104" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000717; Shopify variant id: 44167367950576; Availability: out of stock</t>
         </is>
@@ -19069,12 +19594,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ105" s="3" t="inlineStr">
+      <c r="AQ105" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR105" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR105" s="3" t="inlineStr">
+      <c r="AS105" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000724; Shopify variant id: 44167367983344; Availability: out of stock</t>
         </is>
@@ -19217,12 +19747,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ106" s="3" t="inlineStr">
+      <c r="AQ106" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR106" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR106" s="3" t="inlineStr">
+      <c r="AS106" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000731; Shopify variant id: 44167368016112; Availability: out of stock</t>
         </is>
@@ -19365,12 +19900,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ107" s="3" t="inlineStr">
+      <c r="AQ107" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR107" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR107" s="3" t="inlineStr">
+      <c r="AS107" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000861; Shopify variant id: 44169077981424; Availability: out of stock</t>
         </is>
@@ -19513,12 +20053,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ108" s="3" t="inlineStr">
+      <c r="AQ108" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR108" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR108" s="3" t="inlineStr">
+      <c r="AS108" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006474; Shopify variant id: 47843916579056; Availability: out of stock</t>
         </is>
@@ -19661,12 +20206,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ109" s="3" t="inlineStr">
+      <c r="AQ109" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR109" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR109" s="3" t="inlineStr">
+      <c r="AS109" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000748; Shopify variant id: 44167368048880; Availability: out of stock</t>
         </is>
@@ -19809,12 +20359,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ110" s="3" t="inlineStr">
+      <c r="AQ110" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR110" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR110" s="3" t="inlineStr">
+      <c r="AS110" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000755; Shopify variant id: 44167368081648; Availability: out of stock</t>
         </is>
@@ -19957,12 +20512,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ111" s="3" t="inlineStr">
+      <c r="AQ111" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR111" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR111" s="3" t="inlineStr">
+      <c r="AS111" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000793; Shopify variant id: 44167368114416; Availability: out of stock</t>
         </is>
@@ -20105,12 +20665,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ112" s="3" t="inlineStr">
+      <c r="AQ112" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR112" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR112" s="3" t="inlineStr">
+      <c r="AS112" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000762; Shopify variant id: 44167368147184; Availability: out of stock</t>
         </is>
@@ -20253,12 +20818,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ113" s="3" t="inlineStr">
+      <c r="AQ113" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR113" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR113" s="3" t="inlineStr">
+      <c r="AS113" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000809; Shopify variant id: 44167368179952; Availability: out of stock</t>
         </is>
@@ -20401,12 +20971,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ114" s="3" t="inlineStr">
+      <c r="AQ114" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR114" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR114" s="3" t="inlineStr">
+      <c r="AS114" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000779; Shopify variant id: 44167368212720; Availability: out of stock</t>
         </is>
@@ -20549,12 +21124,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ115" s="3" t="inlineStr">
+      <c r="AQ115" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR115" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR115" s="3" t="inlineStr">
+      <c r="AS115" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000786; Shopify variant id: 44167368245488; Availability: out of stock</t>
         </is>
@@ -20697,12 +21277,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ116" s="3" t="inlineStr">
+      <c r="AQ116" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR116" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR116" s="3" t="inlineStr">
+      <c r="AS116" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000816; Shopify variant id: 44167368278256; Availability: out of stock</t>
         </is>
@@ -20845,12 +21430,17 @@
 From 2026 onward, new batches of rods will be upgraded from Fuji guides to ARK Tangle Free Guides with NanoForce™ Rings.</t>
         </is>
       </c>
-      <c r="AQ117" s="3" t="inlineStr">
+      <c r="AQ117" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR117" s="3" t="inlineStr">
         <is>
           <t>Fuji components / NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR117" s="3" t="inlineStr">
+      <c r="AS117" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000823; Shopify variant id: 44167368311024; Availability: out of stock</t>
         </is>
@@ -20993,12 +21583,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ118" s="4" t="inlineStr">
+      <c r="AQ118" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR118" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR118" s="4" t="inlineStr">
+      <c r="AS118" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006078; Shopify variant id: 46990150598896; Availability: out of stock</t>
         </is>
@@ -21141,12 +21736,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ119" s="4" t="inlineStr">
+      <c r="AQ119" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR119" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR119" s="4" t="inlineStr">
+      <c r="AS119" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006023; Shopify variant id: 46990165803248; Availability: out of stock</t>
         </is>
@@ -21289,12 +21889,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ120" s="4" t="inlineStr">
+      <c r="AQ120" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR120" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR120" s="4" t="inlineStr">
+      <c r="AS120" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006016; Shopify variant id: 46990165836016; Availability: out of stock</t>
         </is>
@@ -21437,12 +22042,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ121" s="4" t="inlineStr">
+      <c r="AQ121" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR121" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR121" s="4" t="inlineStr">
+      <c r="AS121" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006061; Shopify variant id: 46990165868784; Availability: out of stock</t>
         </is>
@@ -21585,12 +22195,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ122" s="4" t="inlineStr">
+      <c r="AQ122" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR122" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR122" s="4" t="inlineStr">
+      <c r="AS122" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006009; Shopify variant id: 46990165901552; Availability: out of stock</t>
         </is>
@@ -21733,12 +22348,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ123" s="4" t="inlineStr">
+      <c r="AQ123" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR123" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR123" s="4" t="inlineStr">
+      <c r="AS123" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005996; Shopify variant id: 46990165934320; Availability: out of stock</t>
         </is>
@@ -21881,12 +22501,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ124" s="4" t="inlineStr">
+      <c r="AQ124" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR124" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR124" s="4" t="inlineStr">
+      <c r="AS124" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005989; Shopify variant id: 46990165967088; Availability: out of stock</t>
         </is>
@@ -22029,12 +22654,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ125" s="4" t="inlineStr">
+      <c r="AQ125" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR125" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR125" s="4" t="inlineStr">
+      <c r="AS125" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005972; Shopify variant id: 46990165999856; Availability: out of stock</t>
         </is>
@@ -22177,12 +22807,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ126" s="4" t="inlineStr">
+      <c r="AQ126" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR126" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR126" s="4" t="inlineStr">
+      <c r="AS126" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005965; Shopify variant id: 46990166032624; Availability: out of stock</t>
         </is>
@@ -22325,12 +22960,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ127" s="4" t="inlineStr">
+      <c r="AQ127" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR127" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR127" s="4" t="inlineStr">
+      <c r="AS127" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005958; Shopify variant id: 46990166065392; Availability: out of stock</t>
         </is>
@@ -22473,12 +23113,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ128" s="4" t="inlineStr">
+      <c r="AQ128" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR128" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR128" s="4" t="inlineStr">
+      <c r="AS128" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005941; Shopify variant id: 46990166098160; Availability: out of stock</t>
         </is>
@@ -22621,12 +23266,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ129" s="4" t="inlineStr">
+      <c r="AQ129" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR129" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR129" s="4" t="inlineStr">
+      <c r="AS129" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006054; Shopify variant id: 46990166130928; Availability: out of stock</t>
         </is>
@@ -22769,12 +23419,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ130" s="4" t="inlineStr">
+      <c r="AQ130" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR130" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR130" s="4" t="inlineStr">
+      <c r="AS130" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006047; Shopify variant id: 46990166163696; Availability: out of stock</t>
         </is>
@@ -22917,12 +23572,17 @@
 Backed by a 5-year limited warranty , the Commander Series offers the reliability and quality that serious anglers demand .</t>
         </is>
       </c>
-      <c r="AQ131" s="4" t="inlineStr">
+      <c r="AQ131" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR131" s="4" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR131" s="4" t="inlineStr">
+      <c r="AS131" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077006030; Shopify variant id: 46990166196464; Availability: out of stock</t>
         </is>
@@ -23066,12 +23726,17 @@
 CMD710MLFS - Collapsible</t>
         </is>
       </c>
-      <c r="AQ132" s="3" t="inlineStr">
+      <c r="AQ132" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR132" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR132" s="3" t="inlineStr">
+      <c r="AS132" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006085; Shopify variant id: 46990183661808; Availability: out of stock</t>
         </is>
@@ -23215,12 +23880,17 @@
 CMD710MLFS - Collapsible</t>
         </is>
       </c>
-      <c r="AQ133" s="3" t="inlineStr">
+      <c r="AQ133" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR133" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR133" s="3" t="inlineStr">
+      <c r="AS133" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006092; Shopify variant id: 46990186381552; Availability: out of stock</t>
         </is>
@@ -23364,12 +24034,17 @@
 CMD710MLFS - Collapsible</t>
         </is>
       </c>
-      <c r="AQ134" s="3" t="inlineStr">
+      <c r="AQ134" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR134" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR134" s="3" t="inlineStr">
+      <c r="AS134" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006108; Shopify variant id: 46990186414320; Availability: out of stock</t>
         </is>
@@ -23513,12 +24188,17 @@
 CMD710MLFS - Collapsible</t>
         </is>
       </c>
-      <c r="AQ135" s="3" t="inlineStr">
+      <c r="AQ135" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR135" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR135" s="3" t="inlineStr">
+      <c r="AS135" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006115; Shopify variant id: 46990186447088; Availability: out of stock</t>
         </is>
@@ -23662,12 +24342,17 @@
 CMD710MLFS - Collapsible</t>
         </is>
       </c>
-      <c r="AQ136" s="3" t="inlineStr">
+      <c r="AQ136" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR136" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / high-modulus carbon blank / EVA handle</t>
         </is>
       </c>
-      <c r="AR136" s="3" t="inlineStr">
+      <c r="AS136" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077006122; Shopify variant id: 46990186479856; Availability: out of stock</t>
         </is>
@@ -23815,12 +24500,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ137" s="4" t="inlineStr">
+      <c r="AQ137" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR137" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR137" s="4" t="inlineStr">
+      <c r="AS137" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659123; Shopify variant id: 42643194151152; Availability: out of stock</t>
         </is>
@@ -23968,12 +24658,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ138" s="4" t="inlineStr">
+      <c r="AQ138" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR138" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR138" s="4" t="inlineStr">
+      <c r="AS138" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659130; Shopify variant id: 42643194183920; Availability: out of stock</t>
         </is>
@@ -24121,12 +24816,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ139" s="4" t="inlineStr">
+      <c r="AQ139" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR139" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR139" s="4" t="inlineStr">
+      <c r="AS139" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964660112; Shopify variant id: 42643194216688; Availability: out of stock</t>
         </is>
@@ -24274,12 +24974,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ140" s="4" t="inlineStr">
+      <c r="AQ140" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR140" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR140" s="4" t="inlineStr">
+      <c r="AS140" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659154; Shopify variant id: 42643194249456; Availability: out of stock</t>
         </is>
@@ -24427,12 +25132,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ141" s="4" t="inlineStr">
+      <c r="AQ141" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR141" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR141" s="4" t="inlineStr">
+      <c r="AS141" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659161; Shopify variant id: 42643194282224; Availability: out of stock</t>
         </is>
@@ -24580,12 +25290,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ142" s="4" t="inlineStr">
+      <c r="AQ142" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR142" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR142" s="4" t="inlineStr">
+      <c r="AS142" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659178; Shopify variant id: 42643194314992; Availability: out of stock</t>
         </is>
@@ -24733,12 +25448,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ143" s="4" t="inlineStr">
+      <c r="AQ143" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR143" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR143" s="4" t="inlineStr">
+      <c r="AS143" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964660105; Shopify variant id: 42643194347760; Availability: out of stock</t>
         </is>
@@ -24886,12 +25606,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ144" s="4" t="inlineStr">
+      <c r="AQ144" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR144" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR144" s="4" t="inlineStr">
+      <c r="AS144" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964660099; Shopify variant id: 42643194380528; Availability: out of stock</t>
         </is>
@@ -25039,12 +25764,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ145" s="4" t="inlineStr">
+      <c r="AQ145" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR145" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR145" s="4" t="inlineStr">
+      <c r="AS145" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659185; Shopify variant id: 42643194413296; Availability: out of stock</t>
         </is>
@@ -25192,12 +25922,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ146" s="4" t="inlineStr">
+      <c r="AQ146" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR146" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR146" s="4" t="inlineStr">
+      <c r="AS146" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659208; Shopify variant id: 42643194478832; Availability: out of stock</t>
         </is>
@@ -25345,12 +26080,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ147" s="4" t="inlineStr">
+      <c r="AQ147" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR147" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR147" s="4" t="inlineStr">
+      <c r="AS147" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659215; Shopify variant id: 42643194511600; Availability: out of stock</t>
         </is>
@@ -25498,12 +26238,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ148" s="4" t="inlineStr">
+      <c r="AQ148" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR148" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR148" s="4" t="inlineStr">
+      <c r="AS148" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659222; Shopify variant id: 42643194544368; Availability: out of stock</t>
         </is>
@@ -25651,12 +26396,17 @@
 Built with high-quality components throughout, the Ark Genesis Series 2pc Casting Rods are fitted with Fuji K concept guides with FazLite inserts for seamless line management and unmatched dependability. Finished with otp of the line Portugal AAAA grade cork and high-density EVA grips, the Ark Genesis Series 2pc Casting Rods make the perfect travel companion.</t>
         </is>
       </c>
-      <c r="AQ149" s="4" t="inlineStr">
+      <c r="AQ149" s="7" t="inlineStr">
+        <is>
+          <t>carbon nano tube reinforcement / Fuji K concept guides / FazLite rings</t>
+        </is>
+      </c>
+      <c r="AR149" s="4" t="inlineStr">
         <is>
           <t>Fuji components / carbon nano tube blank / high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR149" s="4" t="inlineStr">
+      <c r="AS149" s="4" t="inlineStr">
         <is>
           <t>UPC: 649964659239; Shopify variant id: 42643194609904; Availability: out of stock</t>
         </is>
@@ -25797,12 +26547,17 @@
 4. Four new models were added according to the usage during Tharp's fishing season.</t>
         </is>
       </c>
-      <c r="AQ150" s="3" t="inlineStr">
+      <c r="AQ150" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR150" s="3" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR150" s="3" t="inlineStr">
+      <c r="AS150" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000533; Shopify variant id: 44167372013808; Availability: out of stock</t>
         </is>
@@ -25943,12 +26698,17 @@
 4. Four new models were added according to the usage during Tharp's fishing season.</t>
         </is>
       </c>
-      <c r="AQ151" s="3" t="inlineStr">
+      <c r="AQ151" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR151" s="3" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR151" s="3" t="inlineStr">
+      <c r="AS151" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000526; Shopify variant id: 44167372046576; Availability: out of stock</t>
         </is>
@@ -26093,12 +26853,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ152" s="4" t="inlineStr">
+      <c r="AQ152" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR152" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR152" s="4" t="inlineStr">
+      <c r="AS152" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000571; Shopify variant id: 44168959459568; Availability: out of stock</t>
         </is>
@@ -26243,12 +27008,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ153" s="4" t="inlineStr">
+      <c r="AQ153" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR153" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR153" s="4" t="inlineStr">
+      <c r="AS153" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000427; Shopify variant id: 44167371587824; Availability: out of stock</t>
         </is>
@@ -26393,12 +27163,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ154" s="4" t="inlineStr">
+      <c r="AQ154" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR154" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR154" s="4" t="inlineStr">
+      <c r="AS154" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000434; Shopify variant id: 44167371620592; Availability: out of stock</t>
         </is>
@@ -26543,12 +27318,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ155" s="4" t="inlineStr">
+      <c r="AQ155" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR155" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR155" s="4" t="inlineStr">
+      <c r="AS155" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000441; Shopify variant id: 44167371653360; Availability: out of stock</t>
         </is>
@@ -26693,12 +27473,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ156" s="4" t="inlineStr">
+      <c r="AQ156" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR156" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR156" s="4" t="inlineStr">
+      <c r="AS156" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000540; Shopify variant id: 44168959557872; Availability: out of stock</t>
         </is>
@@ -26843,12 +27628,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ157" s="4" t="inlineStr">
+      <c r="AQ157" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR157" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR157" s="4" t="inlineStr">
+      <c r="AS157" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000458; Shopify variant id: 44167371686128; Availability: out of stock</t>
         </is>
@@ -26993,12 +27783,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ158" s="4" t="inlineStr">
+      <c r="AQ158" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR158" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR158" s="4" t="inlineStr">
+      <c r="AS158" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000465; Shopify variant id: 44167371718896; Availability: out of stock</t>
         </is>
@@ -27143,12 +27938,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ159" s="4" t="inlineStr">
+      <c r="AQ159" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR159" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR159" s="4" t="inlineStr">
+      <c r="AS159" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000472; Shopify variant id: 44167371751664; Availability: out of stock</t>
         </is>
@@ -27293,12 +28093,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ160" s="4" t="inlineStr">
+      <c r="AQ160" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR160" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR160" s="4" t="inlineStr">
+      <c r="AS160" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000489; Shopify variant id: 44167371784432; Availability: out of stock</t>
         </is>
@@ -27443,12 +28248,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ161" s="4" t="inlineStr">
+      <c r="AQ161" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR161" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR161" s="4" t="inlineStr">
+      <c r="AS161" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000557; Shopify variant id: 44168959492336; Availability: out of stock</t>
         </is>
@@ -27593,12 +28403,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ162" s="4" t="inlineStr">
+      <c r="AQ162" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR162" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR162" s="4" t="inlineStr">
+      <c r="AS162" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000496; Shopify variant id: 44167371817200; Availability: out of stock</t>
         </is>
@@ -27743,12 +28558,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ163" s="4" t="inlineStr">
+      <c r="AQ163" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR163" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR163" s="4" t="inlineStr">
+      <c r="AS163" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000564; Shopify variant id: 44168959525104; Availability: out of stock</t>
         </is>
@@ -27893,12 +28713,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ164" s="4" t="inlineStr">
+      <c r="AQ164" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR164" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR164" s="4" t="inlineStr">
+      <c r="AS164" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000502; Shopify variant id: 44167371849968; Availability: out of stock</t>
         </is>
@@ -28043,12 +28868,17 @@
 NTS74M-G - Scarface</t>
         </is>
       </c>
-      <c r="AQ165" s="4" t="inlineStr">
+      <c r="AQ165" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Fuji K concept guides / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR165" s="4" t="inlineStr">
         <is>
           <t>Fuji components / high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR165" s="4" t="inlineStr">
+      <c r="AS165" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000519; Shopify variant id: 44167371882736; Availability: out of stock</t>
         </is>
@@ -28192,12 +29022,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ166" s="3" t="inlineStr">
+      <c r="AQ166" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR166" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR166" s="3" t="inlineStr">
+      <c r="AS166" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002421; Shopify variant id: 46715183071472; Availability: out of stock</t>
         </is>
@@ -28341,12 +29176,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ167" s="3" t="inlineStr">
+      <c r="AQ167" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR167" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR167" s="3" t="inlineStr">
+      <c r="AS167" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002438; Shopify variant id: 46715183104240; Availability: out of stock</t>
         </is>
@@ -28490,12 +29330,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ168" s="3" t="inlineStr">
+      <c r="AQ168" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR168" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR168" s="3" t="inlineStr">
+      <c r="AS168" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002445; Shopify variant id: 46715183137008; Availability: out of stock</t>
         </is>
@@ -28639,12 +29484,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ169" s="3" t="inlineStr">
+      <c r="AQ169" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR169" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR169" s="3" t="inlineStr">
+      <c r="AS169" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002452; Shopify variant id: 46715183169776; Availability: out of stock</t>
         </is>
@@ -28788,12 +29638,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ170" s="3" t="inlineStr">
+      <c r="AQ170" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR170" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR170" s="3" t="inlineStr">
+      <c r="AS170" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002469; Shopify variant id: 46715183202544; Availability: out of stock</t>
         </is>
@@ -28937,12 +29792,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ171" s="3" t="inlineStr">
+      <c r="AQ171" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR171" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR171" s="3" t="inlineStr">
+      <c r="AS171" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002476; Shopify variant id: 46715183235312; Availability: out of stock</t>
         </is>
@@ -29086,12 +29946,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ172" s="3" t="inlineStr">
+      <c r="AQ172" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR172" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR172" s="3" t="inlineStr">
+      <c r="AS172" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002483; Shopify variant id: 46715183268080; Availability: out of stock</t>
         </is>
@@ -29235,12 +30100,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ173" s="3" t="inlineStr">
+      <c r="AQ173" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR173" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR173" s="3" t="inlineStr">
+      <c r="AS173" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002490; Shopify variant id: 46715183300848; Availability: out of stock</t>
         </is>
@@ -29384,12 +30254,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ174" s="3" t="inlineStr">
+      <c r="AQ174" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR174" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR174" s="3" t="inlineStr">
+      <c r="AS174" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002506; Shopify variant id: 46715183333616; Availability: out of stock</t>
         </is>
@@ -29533,12 +30408,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ175" s="3" t="inlineStr">
+      <c r="AQ175" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR175" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR175" s="3" t="inlineStr">
+      <c r="AS175" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002513; Shopify variant id: 46715183366384; Availability: out of stock</t>
         </is>
@@ -29682,12 +30562,17 @@
 3A Grade Full Cork Handle for a comfortable, ergonomic grip</t>
         </is>
       </c>
-      <c r="AQ176" s="3" t="inlineStr">
+      <c r="AQ176" s="6" t="inlineStr">
+        <is>
+          <t>ARK HPCR (High Pressure Carbon Fiber Rolling) technology / carbon nano tube reinforcement / ARK Tangle-Free Guides / NanoForce Rings</t>
+        </is>
+      </c>
+      <c r="AR176" s="3" t="inlineStr">
         <is>
           <t>NanoForce guide rings / carbon nano tube blank / high-modulus carbon blank / cork handle</t>
         </is>
       </c>
-      <c r="AR176" s="3" t="inlineStr">
+      <c r="AS176" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002520; Shopify variant id: 46715183399152; Availability: out of stock</t>
         </is>
@@ -29820,12 +30705,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ177" s="4" t="inlineStr">
+      <c r="AQ177" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR177" s="4" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR177" s="4" t="inlineStr">
+      <c r="AS177" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000892; Shopify variant id: 44167369556208; Availability: out of stock</t>
         </is>
@@ -29958,12 +30848,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ178" s="4" t="inlineStr">
+      <c r="AQ178" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR178" s="4" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR178" s="4" t="inlineStr">
+      <c r="AS178" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000908; Shopify variant id: 44167369621744; Availability: out of stock</t>
         </is>
@@ -30096,12 +30991,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ179" s="4" t="inlineStr">
+      <c r="AQ179" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR179" s="4" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR179" s="4" t="inlineStr">
+      <c r="AS179" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077000915; Shopify variant id: 44167369588976; Availability: out of stock</t>
         </is>
@@ -30234,12 +31134,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ180" s="3" t="inlineStr">
+      <c r="AQ180" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR180" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR180" s="3" t="inlineStr">
+      <c r="AS180" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000922; Shopify variant id: 44167369261296; Availability: out of stock</t>
         </is>
@@ -30372,12 +31277,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ181" s="3" t="inlineStr">
+      <c r="AQ181" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR181" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR181" s="3" t="inlineStr">
+      <c r="AS181" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002193; Shopify variant id: 46699196055792; Availability: out of stock</t>
         </is>
@@ -30510,12 +31420,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ182" s="3" t="inlineStr">
+      <c r="AQ182" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR182" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR182" s="3" t="inlineStr">
+      <c r="AS182" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000939; Shopify variant id: 44167369294064; Availability: out of stock</t>
         </is>
@@ -30648,12 +31563,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ183" s="3" t="inlineStr">
+      <c r="AQ183" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR183" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR183" s="3" t="inlineStr">
+      <c r="AS183" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000977; Shopify variant id: 44167369457904; Availability: out of stock</t>
         </is>
@@ -30786,12 +31706,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ184" s="3" t="inlineStr">
+      <c r="AQ184" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR184" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR184" s="3" t="inlineStr">
+      <c r="AS184" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000946; Shopify variant id: 44167369326832; Availability: out of stock</t>
         </is>
@@ -30924,12 +31849,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ185" s="3" t="inlineStr">
+      <c r="AQ185" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR185" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR185" s="3" t="inlineStr">
+      <c r="AS185" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000984; Shopify variant id: 44167369425136; Availability: out of stock</t>
         </is>
@@ -31062,12 +31992,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ186" s="3" t="inlineStr">
+      <c r="AQ186" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR186" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR186" s="3" t="inlineStr">
+      <c r="AS186" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000953; Shopify variant id: 44167369359600; Availability: out of stock</t>
         </is>
@@ -31200,12 +32135,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ187" s="3" t="inlineStr">
+      <c r="AQ187" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR187" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR187" s="3" t="inlineStr">
+      <c r="AS187" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000960; Shopify variant id: 44167369392368; Availability: out of stock</t>
         </is>
@@ -31338,12 +32278,17 @@
           <t>The 3rd gen of Lancer Series rods for 2024. It features: 1. Japanese Toray 40T modulus carbon-fiber with our unique MDML Technology for a lighter, stronger, more sensitive blank. 2. New designed Team ARK reel seat. 3.Black Coated Stainless Micro Guides System With Zirconium Inserts. 4. Weight reduced up to 20%</t>
         </is>
       </c>
-      <c r="AQ188" s="3" t="inlineStr">
+      <c r="AQ188" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Direction Multi-Layer technology / Black Coated Stainless Micro Guides System With Zirconium Inserts / Team ARK reel seat</t>
+        </is>
+      </c>
+      <c r="AR188" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank</t>
         </is>
       </c>
-      <c r="AR188" s="3" t="inlineStr">
+      <c r="AS188" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077000991; Shopify variant id: 44167369490672; Availability: out of stock</t>
         </is>
@@ -31486,12 +32431,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ189" s="4" t="inlineStr">
+      <c r="AQ189" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR189" s="4" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR189" s="4" t="inlineStr">
+      <c r="AS189" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005897; Shopify variant id: 43440042770672; Availability: out of stock</t>
         </is>
@@ -31634,12 +32584,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ190" s="4" t="inlineStr">
+      <c r="AQ190" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR190" s="4" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR190" s="4" t="inlineStr">
+      <c r="AS190" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005903; Shopify variant id: 43440042803440; Availability: out of stock</t>
         </is>
@@ -31782,12 +32737,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ191" s="4" t="inlineStr">
+      <c r="AQ191" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR191" s="4" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR191" s="4" t="inlineStr">
+      <c r="AS191" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005934; Shopify variant id: 47359917916400; Availability: out of stock</t>
         </is>
@@ -31930,12 +32890,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ192" s="4" t="inlineStr">
+      <c r="AQ192" s="7" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR192" s="4" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR192" s="4" t="inlineStr">
+      <c r="AS192" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077005910; Shopify variant id: 42643164922096; Availability: out of stock</t>
         </is>
@@ -32078,12 +33043,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ193" s="3" t="inlineStr">
+      <c r="AQ193" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR193" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR193" s="3" t="inlineStr">
+      <c r="AS193" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005781; Shopify variant id: 42643181633776; Availability: out of stock</t>
         </is>
@@ -32226,12 +33196,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ194" s="3" t="inlineStr">
+      <c r="AQ194" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR194" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR194" s="3" t="inlineStr">
+      <c r="AS194" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005798; Shopify variant id: 42643181666544; Availability: out of stock</t>
         </is>
@@ -32374,12 +33349,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ195" s="3" t="inlineStr">
+      <c r="AQ195" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR195" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR195" s="3" t="inlineStr">
+      <c r="AS195" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005804; Shopify variant id: 42643181699312; Availability: out of stock</t>
         </is>
@@ -32522,12 +33502,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ196" s="3" t="inlineStr">
+      <c r="AQ196" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR196" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR196" s="3" t="inlineStr">
+      <c r="AS196" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005811; Shopify variant id: 42643181732080; Availability: out of stock</t>
         </is>
@@ -32670,12 +33655,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ197" s="3" t="inlineStr">
+      <c r="AQ197" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR197" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR197" s="3" t="inlineStr">
+      <c r="AS197" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005828; Shopify variant id: 42643181764848; Availability: out of stock</t>
         </is>
@@ -32818,12 +33808,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ198" s="3" t="inlineStr">
+      <c r="AQ198" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR198" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR198" s="3" t="inlineStr">
+      <c r="AS198" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005927; Shopify variant id: 47359689457904; Availability: out of stock</t>
         </is>
@@ -32966,12 +33961,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ199" s="3" t="inlineStr">
+      <c r="AQ199" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR199" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR199" s="3" t="inlineStr">
+      <c r="AS199" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005835; Shopify variant id: 42643181797616; Availability: out of stock</t>
         </is>
@@ -33114,12 +34114,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ200" s="3" t="inlineStr">
+      <c r="AQ200" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR200" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR200" s="3" t="inlineStr">
+      <c r="AS200" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005842; Shopify variant id: 42643181830384; Availability: out of stock</t>
         </is>
@@ -33262,12 +34267,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ201" s="3" t="inlineStr">
+      <c r="AQ201" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR201" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR201" s="3" t="inlineStr">
+      <c r="AS201" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005859; Shopify variant id: 42643181863152; Availability: out of stock</t>
         </is>
@@ -33410,12 +34420,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ202" s="3" t="inlineStr">
+      <c r="AQ202" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR202" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR202" s="3" t="inlineStr">
+      <c r="AS202" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005866; Shopify variant id: 42643181895920; Availability: out of stock</t>
         </is>
@@ -33558,12 +34573,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ203" s="3" t="inlineStr">
+      <c r="AQ203" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR203" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR203" s="3" t="inlineStr">
+      <c r="AS203" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005873; Shopify variant id: 42643181928688; Availability: out of stock</t>
         </is>
@@ -33706,12 +34726,17 @@
 Despite its premium features , the Cobb Series maintains an unbeatable $99.99 retail price , backed by a 5-year limited warranty -offering unmatched value for serious anglers.</t>
         </is>
       </c>
-      <c r="AQ204" s="3" t="inlineStr">
+      <c r="AQ204" s="6" t="inlineStr">
+        <is>
+          <t>ARK Stainless Steel Tangle-Free Guides / A-Ring technology</t>
+        </is>
+      </c>
+      <c r="AR204" s="3" t="inlineStr">
         <is>
           <t>high-modulus carbon blank / cork handle / EVA handle</t>
         </is>
       </c>
-      <c r="AR204" s="3" t="inlineStr">
+      <c r="AS204" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077005880; Shopify variant id: 42643181961456; Availability: out of stock</t>
         </is>
@@ -33848,12 +34873,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ205" s="4" t="inlineStr">
+      <c r="AQ205" s="7" t="inlineStr"/>
+      <c r="AR205" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR205" s="4" t="inlineStr">
+      <c r="AS205" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002537; Shopify variant id: 47010395750640; Availability: out of stock</t>
         </is>
@@ -33990,12 +35016,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ206" s="4" t="inlineStr">
+      <c r="AQ206" s="7" t="inlineStr"/>
+      <c r="AR206" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR206" s="4" t="inlineStr">
+      <c r="AS206" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002544; Shopify variant id: 47010395783408; Availability: out of stock</t>
         </is>
@@ -34132,12 +35159,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ207" s="4" t="inlineStr">
+      <c r="AQ207" s="7" t="inlineStr"/>
+      <c r="AR207" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR207" s="4" t="inlineStr">
+      <c r="AS207" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002551; Shopify variant id: 47010395816176; Availability: out of stock</t>
         </is>
@@ -34274,12 +35302,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ208" s="4" t="inlineStr">
+      <c r="AQ208" s="7" t="inlineStr"/>
+      <c r="AR208" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR208" s="4" t="inlineStr">
+      <c r="AS208" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002568; Shopify variant id: 47010395848944; Availability: out of stock</t>
         </is>
@@ -34416,12 +35445,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ209" s="4" t="inlineStr">
+      <c r="AQ209" s="7" t="inlineStr"/>
+      <c r="AR209" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR209" s="4" t="inlineStr">
+      <c r="AS209" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002575; Shopify variant id: 47010395881712; Availability: out of stock</t>
         </is>
@@ -34558,12 +35588,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ210" s="4" t="inlineStr">
+      <c r="AQ210" s="7" t="inlineStr"/>
+      <c r="AR210" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR210" s="4" t="inlineStr">
+      <c r="AS210" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002582; Shopify variant id: 47010395914480; Availability: out of stock</t>
         </is>
@@ -34700,12 +35731,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ211" s="4" t="inlineStr">
+      <c r="AQ211" s="7" t="inlineStr"/>
+      <c r="AR211" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR211" s="4" t="inlineStr">
+      <c r="AS211" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077003770; Shopify variant id: 47010395947248; Availability: out of stock</t>
         </is>
@@ -34842,12 +35874,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ212" s="4" t="inlineStr">
+      <c r="AQ212" s="7" t="inlineStr"/>
+      <c r="AR212" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR212" s="4" t="inlineStr">
+      <c r="AS212" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002599; Shopify variant id: 47010395980016; Availability: out of stock</t>
         </is>
@@ -34984,12 +36017,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ213" s="4" t="inlineStr">
+      <c r="AQ213" s="7" t="inlineStr"/>
+      <c r="AR213" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR213" s="4" t="inlineStr">
+      <c r="AS213" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002605; Shopify variant id: 47010396012784; Availability: out of stock</t>
         </is>
@@ -35126,12 +36160,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ214" s="3" t="inlineStr">
+      <c r="AQ214" s="6" t="inlineStr"/>
+      <c r="AR214" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR214" s="3" t="inlineStr">
+      <c r="AS214" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002582; Shopify variant id: 47347668484336; Availability: out of stock</t>
         </is>
@@ -35268,12 +36303,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ215" s="3" t="inlineStr">
+      <c r="AQ215" s="6" t="inlineStr"/>
+      <c r="AR215" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR215" s="3" t="inlineStr">
+      <c r="AS215" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077003770; Shopify variant id: 47347669041392; Availability: out of stock</t>
         </is>
@@ -35410,12 +36446,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ216" s="3" t="inlineStr">
+      <c r="AQ216" s="6" t="inlineStr"/>
+      <c r="AR216" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR216" s="3" t="inlineStr">
+      <c r="AS216" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662147; Shopify variant id: 43444561182960; Availability: out of stock</t>
         </is>
@@ -35552,12 +36589,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ217" s="3" t="inlineStr">
+      <c r="AQ217" s="6" t="inlineStr"/>
+      <c r="AR217" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR217" s="3" t="inlineStr">
+      <c r="AS217" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662154; Shopify variant id: 43431609073904; Availability: out of stock</t>
         </is>
@@ -35694,12 +36732,13 @@
           <t>ARK Catalyzer series rods are offering professional-grade performance at a very affordable price. It will be the perfect start-up rod for everyone, no matter you are a big-dream-chaser or just having fun with the family. Employing the 36-TON High Modulus carbon fiber blank with ARK custom reel seat, stainless steel guides, and high-density EVA Grips, The Catalyzer is no doubt the lightest and most sensitive rod at this price range.Warranty:90Days with the dated purchase receipt.</t>
         </is>
       </c>
-      <c r="AQ218" s="3" t="inlineStr">
+      <c r="AQ218" s="6" t="inlineStr"/>
+      <c r="AR218" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR218" s="3" t="inlineStr">
+      <c r="AS218" s="3" t="inlineStr">
         <is>
           <t>UPC: 649964662161; Shopify variant id: 43439992668400; Availability: out of stock</t>
         </is>
@@ -35824,12 +36863,17 @@
           <t>The Catalyzer Series Ice Rod features a premium solid carbon blank and Custom polymer split grips. Lightweight stainless steel guides on this rod stand up to harsh conditions. High-Visibility Strike Indicator* detects even the slightest bites beneath the ice! Designed for versatility, this series is perfect for a range of ice fishing styles and techniques, targeting panfish, trout, and walleye. Lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ219" s="4" t="inlineStr">
+      <c r="AQ219" s="7" t="inlineStr">
+        <is>
+          <t>High-Visibility Strike Indicator</t>
+        </is>
+      </c>
+      <c r="AR219" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR219" s="4" t="inlineStr">
+      <c r="AS219" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002230; Shopify variant id: 46714962084080; Availability: out of stock</t>
         </is>
@@ -35954,12 +36998,17 @@
           <t>The Catalyzer Series Ice Rod features a premium solid carbon blank and Custom polymer split grips. Lightweight stainless steel guides on this rod stand up to harsh conditions. High-Visibility Strike Indicator* detects even the slightest bites beneath the ice! Designed for versatility, this series is perfect for a range of ice fishing styles and techniques, targeting panfish, trout, and walleye. Lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ220" s="4" t="inlineStr">
+      <c r="AQ220" s="7" t="inlineStr">
+        <is>
+          <t>High-Visibility Strike Indicator</t>
+        </is>
+      </c>
+      <c r="AR220" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR220" s="4" t="inlineStr">
+      <c r="AS220" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002247; Shopify variant id: 46714962116848; Availability: out of stock</t>
         </is>
@@ -36084,12 +37133,17 @@
           <t>The Catalyzer Series Ice Rod features a premium solid carbon blank and Custom polymer split grips. Lightweight stainless steel guides on this rod stand up to harsh conditions. High-Visibility Strike Indicator* detects even the slightest bites beneath the ice! Designed for versatility, this series is perfect for a range of ice fishing styles and techniques, targeting panfish, trout, and walleye. Lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ221" s="4" t="inlineStr">
+      <c r="AQ221" s="7" t="inlineStr">
+        <is>
+          <t>High-Visibility Strike Indicator</t>
+        </is>
+      </c>
+      <c r="AR221" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR221" s="4" t="inlineStr">
+      <c r="AS221" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002254; Shopify variant id: 46714962149616; Availability: out of stock</t>
         </is>
@@ -36214,12 +37268,17 @@
           <t>The Catalyzer Series Ice Rod features a premium solid carbon blank and Custom polymer split grips. Lightweight stainless steel guides on this rod stand up to harsh conditions. High-Visibility Strike Indicator* detects even the slightest bites beneath the ice! Designed for versatility, this series is perfect for a range of ice fishing styles and techniques, targeting panfish, trout, and walleye. Lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ222" s="4" t="inlineStr">
+      <c r="AQ222" s="7" t="inlineStr">
+        <is>
+          <t>High-Visibility Strike Indicator</t>
+        </is>
+      </c>
+      <c r="AR222" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR222" s="4" t="inlineStr">
+      <c r="AS222" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002261; Shopify variant id: 46714962182384; Availability: out of stock</t>
         </is>
@@ -36344,12 +37403,17 @@
           <t>The Catalyzer Series Ice Rod features a premium solid carbon blank and Custom polymer split grips. Lightweight stainless steel guides on this rod stand up to harsh conditions. High-Visibility Strike Indicator* detects even the slightest bites beneath the ice! Designed for versatility, this series is perfect for a range of ice fishing styles and techniques, targeting panfish, trout, and walleye. Lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ223" s="4" t="inlineStr">
+      <c r="AQ223" s="7" t="inlineStr">
+        <is>
+          <t>High-Visibility Strike Indicator</t>
+        </is>
+      </c>
+      <c r="AR223" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR223" s="4" t="inlineStr">
+      <c r="AS223" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002278; Shopify variant id: 46714962215152; Availability: out of stock</t>
         </is>
@@ -36474,12 +37538,17 @@
           <t>The Catalyzer Series Ice Rod features a premium solid carbon blank and Custom polymer split grips. Lightweight stainless steel guides on this rod stand up to harsh conditions. High-Visibility Strike Indicator* detects even the slightest bites beneath the ice! Designed for versatility, this series is perfect for a range of ice fishing styles and techniques, targeting panfish, trout, and walleye. Lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ224" s="4" t="inlineStr">
+      <c r="AQ224" s="7" t="inlineStr">
+        <is>
+          <t>High-Visibility Strike Indicator</t>
+        </is>
+      </c>
+      <c r="AR224" s="4" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR224" s="4" t="inlineStr">
+      <c r="AS224" s="4" t="inlineStr">
         <is>
           <t>UPC: 724077002285; Shopify variant id: 46714962247920; Availability: out of stock</t>
         </is>
@@ -36604,12 +37673,13 @@
           <t>The CORE Series Ice Rod features a Custom Solid Carbon Blank, offering Great sensitivity while maintaining plenty of power. Built to withstand harsh conditions, its lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ225" s="3" t="inlineStr">
+      <c r="AQ225" s="6" t="inlineStr"/>
+      <c r="AR225" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR225" s="3" t="inlineStr">
+      <c r="AS225" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002209; Shopify variant id: 46714852573424; Availability: out of stock</t>
         </is>
@@ -36734,12 +37804,13 @@
           <t>The CORE Series Ice Rod features a Custom Solid Carbon Blank, offering Great sensitivity while maintaining plenty of power. Built to withstand harsh conditions, its lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ226" s="3" t="inlineStr">
+      <c r="AQ226" s="6" t="inlineStr"/>
+      <c r="AR226" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR226" s="3" t="inlineStr">
+      <c r="AS226" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002216; Shopify variant id: 46714852606192; Availability: out of stock</t>
         </is>
@@ -36864,12 +37935,13 @@
           <t>The CORE Series Ice Rod features a Custom Solid Carbon Blank, offering Great sensitivity while maintaining plenty of power. Built to withstand harsh conditions, its lightweight stainless steel guides ensure durability. The rod also boasts a Custom full-grip EVA handle for comfortable and reliable control.</t>
         </is>
       </c>
-      <c r="AQ227" s="3" t="inlineStr">
+      <c r="AQ227" s="6" t="inlineStr"/>
+      <c r="AR227" s="3" t="inlineStr">
         <is>
           <t>EVA handle</t>
         </is>
       </c>
-      <c r="AR227" s="3" t="inlineStr">
+      <c r="AS227" s="3" t="inlineStr">
         <is>
           <t>UPC: 724077002223; Shopify variant id: 46714852638960; Availability: out of stock</t>
         </is>
